--- a/historico_descuentos.xlsx
+++ b/historico_descuentos.xlsx
@@ -4129,7 +4129,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4895,9 +4895,124 @@
         <v>Zona 2_x000d_</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B20" t="str">
+        <v>AMINA MAHMAD ABDEL (COMERCIAL ZITAWI MAHMAD F.P.)</v>
+      </c>
+      <c r="C20" t="str">
+        <v>FACTF/2026/11712</v>
+      </c>
+      <c r="D20" t="str">
+        <v>OEG-4BTE</v>
+      </c>
+      <c r="E20" t="str">
+        <v>1</v>
+      </c>
+      <c r="F20" t="str">
+        <v>115,00</v>
+      </c>
+      <c r="G20" t="str">
+        <v>103,50</v>
+      </c>
+      <c r="H20" t="str">
+        <v>11,50</v>
+      </c>
+      <c r="I20" t="str">
+        <v>11,50</v>
+      </c>
+      <c r="J20" t="str">
+        <v>10%</v>
+      </c>
+      <c r="K20" t="str">
+        <v xml:space="preserve">Critico </v>
+      </c>
+      <c r="L20" t="str">
+        <v>Zona 3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B21" t="str">
+        <v>DISTRIBUIDORA AMADO 2020, C.A.</v>
+      </c>
+      <c r="C21" t="str">
+        <v>FACTF/2026/09790</v>
+      </c>
+      <c r="D21" t="str">
+        <v>OCH-198W</v>
+      </c>
+      <c r="E21" t="str">
+        <v>1</v>
+      </c>
+      <c r="F21" t="str">
+        <v>220,00</v>
+      </c>
+      <c r="G21" t="str">
+        <v>204,60</v>
+      </c>
+      <c r="H21" t="str">
+        <v>15,40</v>
+      </c>
+      <c r="I21" t="str">
+        <v>15,40</v>
+      </c>
+      <c r="J21" t="str">
+        <v>7%</v>
+      </c>
+      <c r="K21" t="str">
+        <v xml:space="preserve">Critico </v>
+      </c>
+      <c r="L21" t="str">
+        <v>Zona 1_x000d_</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B22" t="str">
+        <v>INVERSIONES CASANOVA ELECTRONIC 2009, C.A</v>
+      </c>
+      <c r="C22" t="str">
+        <v>FACTF/2026/09108</v>
+      </c>
+      <c r="D22" t="str">
+        <v>OCH-198W</v>
+      </c>
+      <c r="E22" t="str">
+        <v>1</v>
+      </c>
+      <c r="F22" t="str">
+        <v>220,00</v>
+      </c>
+      <c r="G22" t="str">
+        <v>204,60</v>
+      </c>
+      <c r="H22" t="str">
+        <v>15,40</v>
+      </c>
+      <c r="I22" t="str">
+        <v>15,40</v>
+      </c>
+      <c r="J22" t="str">
+        <v>7%</v>
+      </c>
+      <c r="K22" t="str">
+        <v xml:space="preserve">Critico </v>
+      </c>
+      <c r="L22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Zona 1
+</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/historico_descuentos.xlsx
+++ b/historico_descuentos.xlsx
@@ -4129,7 +4129,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z36"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5006,13 +5006,513 @@
         <v xml:space="preserve">Critico </v>
       </c>
       <c r="L22" t="str" xml:space="preserve">
-        <v xml:space="preserve">Zona 1
+        <v xml:space="preserve">Zona 1_x000d_
 </v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B23" t="str">
+        <v xml:space="preserve">MUEBLES CARIBE &amp; HOGAR C,A </v>
+      </c>
+      <c r="C23" t="str">
+        <v>FACTF/2026/10354</v>
+      </c>
+      <c r="D23" t="str">
+        <v>OEG-4WTE</v>
+      </c>
+      <c r="E23" t="str">
+        <v>2</v>
+      </c>
+      <c r="F23" t="str">
+        <v>115.00</v>
+      </c>
+      <c r="G23" t="str">
+        <v>103.50</v>
+      </c>
+      <c r="H23" t="str">
+        <v>11.50</v>
+      </c>
+      <c r="I23" t="str">
+        <v>23.00</v>
+      </c>
+      <c r="J23" t="str">
+        <v>10%</v>
+      </c>
+      <c r="K23" t="str">
+        <v xml:space="preserve">Critico </v>
+      </c>
+      <c r="L23" t="str">
+        <v>Zona 3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B24" t="str">
+        <v>REMATES POPULARES DE ACARIGUA, C.A.</v>
+      </c>
+      <c r="C24" t="str">
+        <v>FACTF/2026/06629</v>
+      </c>
+      <c r="D24" t="str">
+        <v>OEG-4GTE</v>
+      </c>
+      <c r="E24" t="str">
+        <v>3</v>
+      </c>
+      <c r="F24" t="str">
+        <v>115.00</v>
+      </c>
+      <c r="G24" t="str">
+        <v>103.50</v>
+      </c>
+      <c r="H24" t="str">
+        <v>11.50</v>
+      </c>
+      <c r="I24" t="str">
+        <v>34.50</v>
+      </c>
+      <c r="J24" t="str">
+        <v>10%</v>
+      </c>
+      <c r="K24" t="str">
+        <v xml:space="preserve">Critico </v>
+      </c>
+      <c r="L24" t="str">
+        <v>Zona 3</v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B25" t="str">
+        <v>SURTI HOGAR NEVERI, C.A.</v>
+      </c>
+      <c r="C25" t="str">
+        <v>FACTF/2026/10924</v>
+      </c>
+      <c r="D25" t="str">
+        <v>OEG-4BTE</v>
+      </c>
+      <c r="E25" t="str">
+        <v>6</v>
+      </c>
+      <c r="F25" t="str">
+        <v>115.00</v>
+      </c>
+      <c r="G25" t="str">
+        <v>109.25</v>
+      </c>
+      <c r="H25" t="str">
+        <v>5.75</v>
+      </c>
+      <c r="I25" t="str">
+        <v>34.50</v>
+      </c>
+      <c r="J25" t="str">
+        <v>5%</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Moderado</v>
+      </c>
+      <c r="L25" t="str" xml:space="preserve">
+        <v xml:space="preserve">Zona 2_x000d_
+</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B26" t="str">
+        <v>SURTI HOGAR NEVERI, C.A.</v>
+      </c>
+      <c r="C26" t="str">
+        <v>FACTF/2026/10924</v>
+      </c>
+      <c r="D26" t="str">
+        <v>OEG-4GTE</v>
+      </c>
+      <c r="E26" t="str">
+        <v>6</v>
+      </c>
+      <c r="F26" t="str">
+        <v>115.00</v>
+      </c>
+      <c r="G26" t="str">
+        <v>109.25</v>
+      </c>
+      <c r="H26" t="str">
+        <v>5.75</v>
+      </c>
+      <c r="I26" t="str">
+        <v>34.50</v>
+      </c>
+      <c r="J26" t="str">
+        <v>5%</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Moderado</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Zona 2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v xml:space="preserve">MUEBLERIA LA SIRIA, C.A </v>
+      </c>
+      <c r="C27" t="str">
+        <v>FACTF/2026/12037</v>
+      </c>
+      <c r="D27" t="str">
+        <v>OEG-4WTE</v>
+      </c>
+      <c r="E27" t="str">
+        <v>1</v>
+      </c>
+      <c r="F27" t="str">
+        <v>115</v>
+      </c>
+      <c r="G27" t="str">
+        <v>106.95</v>
+      </c>
+      <c r="H27" t="str">
+        <v>8.05</v>
+      </c>
+      <c r="I27" t="str">
+        <v>8.05</v>
+      </c>
+      <c r="J27" t="str">
+        <v>7%</v>
+      </c>
+      <c r="K27" t="str">
+        <v xml:space="preserve">Critico </v>
+      </c>
+      <c r="L27" t="str">
+        <v>Zona 1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B28" t="str">
+        <v>INVERSIONES MI BENDICION M&amp;G, C.A</v>
+      </c>
+      <c r="C28" t="str">
+        <v>FACTF/2026/12032</v>
+      </c>
+      <c r="D28" t="str">
+        <v>OEG-6ITM</v>
+      </c>
+      <c r="E28" t="str">
+        <v>1</v>
+      </c>
+      <c r="F28" t="str">
+        <v>249</v>
+      </c>
+      <c r="G28" t="str">
+        <v>236.55</v>
+      </c>
+      <c r="H28" t="str">
+        <v>12.45</v>
+      </c>
+      <c r="I28" t="str">
+        <v>12.45</v>
+      </c>
+      <c r="J28" t="str">
+        <v>5%</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Moderado</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Zona 2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B29" t="str">
+        <v>MUEBLEGANGA ELECTRONICA, C.A</v>
+      </c>
+      <c r="C29" t="str">
+        <v>FACTF/2026/12481</v>
+      </c>
+      <c r="D29" t="str">
+        <v>OEG-4WTE</v>
+      </c>
+      <c r="E29" t="str">
+        <v>1</v>
+      </c>
+      <c r="F29" t="str">
+        <v>115</v>
+      </c>
+      <c r="G29" t="str">
+        <v>106.95</v>
+      </c>
+      <c r="H29" t="str">
+        <v>8.05</v>
+      </c>
+      <c r="I29" t="str">
+        <v>8.05</v>
+      </c>
+      <c r="J29" t="str">
+        <v>7%</v>
+      </c>
+      <c r="K29" t="str">
+        <v xml:space="preserve">Critico </v>
+      </c>
+      <c r="L29" t="str">
+        <v>Zona 1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B30" t="str">
+        <v>SUGEL ABOU HADDOUR ABO HADDOUR (ABOU HADDOUR BIG STORE, F.P)</v>
+      </c>
+      <c r="C30" t="str">
+        <v>FACTF/2026/11759</v>
+      </c>
+      <c r="D30" t="str">
+        <v>OEG-4BTE</v>
+      </c>
+      <c r="E30" t="str">
+        <v>1</v>
+      </c>
+      <c r="F30" t="str">
+        <v>110</v>
+      </c>
+      <c r="G30" t="str">
+        <v>102.3</v>
+      </c>
+      <c r="H30" t="str">
+        <v>7.7</v>
+      </c>
+      <c r="I30" t="str">
+        <v>7.7</v>
+      </c>
+      <c r="J30" t="str">
+        <v>7%</v>
+      </c>
+      <c r="K30" t="str">
+        <v xml:space="preserve">Critico </v>
+      </c>
+      <c r="L30" t="str">
+        <v>Zona 1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B31" t="str">
+        <v>REMATES POPULARES DE ACARIGUA, C.A</v>
+      </c>
+      <c r="C31" t="str">
+        <v>FACTF/2026/06890</v>
+      </c>
+      <c r="D31" t="str">
+        <v>OCH-198W</v>
+      </c>
+      <c r="E31" t="str">
+        <v>1</v>
+      </c>
+      <c r="F31" t="str">
+        <v>190</v>
+      </c>
+      <c r="G31" t="str">
+        <v>171</v>
+      </c>
+      <c r="H31" t="str">
+        <v>19</v>
+      </c>
+      <c r="I31" t="str">
+        <v>19</v>
+      </c>
+      <c r="J31" t="str">
+        <v>10%</v>
+      </c>
+      <c r="K31" t="str">
+        <v xml:space="preserve">Critico </v>
+      </c>
+      <c r="L31" t="str">
+        <v>Zona 2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B32" t="str">
+        <v>REMATES POPULARES DE ACARIGUA, C.A</v>
+      </c>
+      <c r="C32" t="str">
+        <v>FACTF/2026/06629</v>
+      </c>
+      <c r="D32" t="str">
+        <v>OEG-4GTE</v>
+      </c>
+      <c r="E32" t="str">
+        <v>1</v>
+      </c>
+      <c r="F32" t="str">
+        <v>115</v>
+      </c>
+      <c r="G32" t="str">
+        <v>103.5</v>
+      </c>
+      <c r="H32" t="str">
+        <v>11.5</v>
+      </c>
+      <c r="I32" t="str">
+        <v>11.5</v>
+      </c>
+      <c r="J32" t="str">
+        <v>10%</v>
+      </c>
+      <c r="K32" t="str">
+        <v xml:space="preserve">Critico </v>
+      </c>
+      <c r="L32" t="str">
+        <v>Zona 2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B33" t="str">
+        <v>MLK STORE, C.A.</v>
+      </c>
+      <c r="C33" t="str">
+        <v>FACTF/2026/12212</v>
+      </c>
+      <c r="D33" t="str">
+        <v>OEG-4BTE</v>
+      </c>
+      <c r="E33" t="str">
+        <v>2</v>
+      </c>
+      <c r="F33" t="str">
+        <v>115,00</v>
+      </c>
+      <c r="G33" t="str">
+        <v>103,50</v>
+      </c>
+      <c r="H33" t="str">
+        <v>11,50</v>
+      </c>
+      <c r="I33" t="str">
+        <v>23,00_x000d_</v>
+      </c>
+      <c r="J33" t="str">
+        <v>10%</v>
+      </c>
+      <c r="K33" t="str">
+        <v xml:space="preserve">Critico </v>
+      </c>
+      <c r="L33" t="str">
+        <v>Zona 2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B34" t="str">
+        <v>MLK STORE, C.A.</v>
+      </c>
+      <c r="C34" t="str">
+        <v>FACTF/2026/12212</v>
+      </c>
+      <c r="D34" t="str">
+        <v>OEG-4WTE</v>
+      </c>
+      <c r="E34" t="str">
+        <v>2</v>
+      </c>
+      <c r="F34" t="str">
+        <v>115,00</v>
+      </c>
+      <c r="G34" t="str">
+        <v>103,50</v>
+      </c>
+      <c r="H34" t="str">
+        <v>11,50</v>
+      </c>
+      <c r="I34" t="str">
+        <v>23,00_x000d_</v>
+      </c>
+      <c r="J34" t="str">
+        <v>10%</v>
+      </c>
+      <c r="K34" t="str">
+        <v xml:space="preserve">Critico </v>
+      </c>
+      <c r="L34" t="str">
+        <v>Zona 2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Septiembre 2026</v>
+      </c>
+      <c r="B35" t="str">
+        <v>MLK STORE, C.A.</v>
+      </c>
+      <c r="C35" t="str">
+        <v>FACTF/2026/12212</v>
+      </c>
+      <c r="D35" t="str">
+        <v>OEG-4GTE</v>
+      </c>
+      <c r="E35" t="str">
+        <v>1</v>
+      </c>
+      <c r="F35" t="str">
+        <v>115,00</v>
+      </c>
+      <c r="G35" t="str">
+        <v>103,50</v>
+      </c>
+      <c r="H35" t="str">
+        <v>11,50</v>
+      </c>
+      <c r="I35" t="str">
+        <v>11,5_x000d_</v>
+      </c>
+      <c r="J35" t="str">
+        <v>10%</v>
+      </c>
+      <c r="K35" t="str">
+        <v xml:space="preserve">Critico </v>
+      </c>
+      <c r="L35" t="str">
+        <v>Zona 2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z36"/>
   </ignoredErrors>
 </worksheet>
 </file>